--- a/output/2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -652,10 +652,9 @@
           <t>+386 2 620 97 94</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sistemi di depolverazione industriale, filtrazione fumi/nebbie oleose; sede reale in Podravska, copertura specifica su Savinjska non confermata da fonti esterne</t>
+          <t>Sistemi di depolverazione industriale, filtrazione fumi/nebbie oleose; sede reale in Podravska, copertura specifica su Savinjska non confermata da fonti esterne [DUPLICATO — vedi anche: 2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -744,7 +743,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -786,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -828,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -870,7 +869,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -912,7 +911,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -954,7 +953,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -996,7 +995,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1037,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1079,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1116,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Agente Donaldson Torit DCE, oltre 30 anni di esperienza in filtrazione industriale</t>
+          <t>Agente Donaldson Torit DCE, oltre 30 anni di esperienza in filtrazione industriale [DUPLICATO — vedi anche: 2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1164,7 +1163,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
